--- a/Shared/XLS/BattlePower.xlsx
+++ b/Shared/XLS/BattlePower.xlsx
@@ -1,80 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
   </bookViews>
   <sheets>
-    <sheet name="#BattlePower_Stat" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="#BattlePower_Option" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="#BattlePower_Stat" sheetId="1" r:id="rId1"/>
+    <sheet name="#BattlePower_Option" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+  <si>
+    <t>!Table</t>
+  </si>
+  <si>
+    <t>BattlePower_Stat</t>
+  </si>
+  <si>
+    <t>!ID</t>
+  </si>
+  <si>
+    <t>SourceStat</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>!int</t>
+  </si>
+  <si>
+    <t>!Stat</t>
+  </si>
+  <si>
+    <t>!float</t>
+  </si>
+  <si>
+    <t>Stat_Atk</t>
+  </si>
+  <si>
+    <t>Stat_AtkSpeed</t>
+  </si>
+  <si>
+    <t>Stat_CritRate</t>
+  </si>
+  <si>
+    <t>Stat_CritDamage</t>
+  </si>
+  <si>
+    <t>Stat_DamageBonus</t>
+  </si>
+  <si>
+    <t>Stat_MeleeDamageBonus</t>
+  </si>
+  <si>
+    <t>Stat_RangeDamageBonus</t>
+  </si>
+  <si>
+    <t>Stat_BossDamageBonus</t>
+  </si>
+  <si>
+    <t>Stat_FinalDamageAmp</t>
+  </si>
+  <si>
+    <t>Stat_DefPen</t>
+  </si>
+  <si>
+    <t>Stat_MaxHp</t>
+  </si>
+  <si>
+    <t>Stat_HpRegen</t>
+  </si>
+  <si>
+    <t>Stat_Def</t>
+  </si>
+  <si>
+    <t>Stat_DamageReduction</t>
+  </si>
+  <si>
+    <t>Stat_LifeOnHit</t>
+  </si>
+  <si>
+    <t>Stat_EvasionRate</t>
+  </si>
+  <si>
+    <t>Stat_BlockRate</t>
+  </si>
+  <si>
+    <t>Stat_MoveSpeed</t>
+  </si>
+  <si>
+    <t>BattlePower_Option</t>
+  </si>
+  <si>
+    <t>SourceOption</t>
+  </si>
+  <si>
+    <t>Point</t>
+  </si>
+  <si>
+    <t>!Option</t>
+  </si>
+  <si>
+    <t>OPT_LEARN_DualBlades_Active_01</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
-      <family val="2"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -86,7 +183,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.5999938962981048"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -134,118 +231,56 @@
     </border>
   </borders>
   <cellStyleXfs count="4">
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
+    <cellStyle name="40% - 강조색3" xfId="2" builtinId="39"/>
+    <cellStyle name="좋음" xfId="1" builtinId="26"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="좋음" xfId="1" builtinId="26"/>
-    <cellStyle name="40% - 강조색3" xfId="2" builtinId="39"/>
     <cellStyle name="표준 2" xfId="3"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -504,446 +539,368 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="11.625" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
-    <col width="16.25" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
-    <col width="23.75" customWidth="1" style="1" min="3" max="3"/>
-    <col width="16.25" customWidth="1" style="1" min="4" max="4"/>
-    <col width="16.5" customWidth="1" style="1" min="5" max="5"/>
-    <col width="13.75" customWidth="1" style="1" min="6" max="6"/>
-    <col width="13.625" customWidth="1" style="1" min="7" max="7"/>
-    <col width="18.5" customWidth="1" style="1" min="8" max="8"/>
-    <col width="9" customWidth="1" style="1" min="9" max="9"/>
-    <col width="9" customWidth="1" style="1" min="10" max="16384"/>
+    <col min="1" max="1" width="11.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5" style="1" customWidth="1"/>
+    <col min="9" max="10" width="9" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" s="3">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>!Table</t>
-        </is>
-      </c>
-      <c r="B1" s="9" t="inlineStr">
-        <is>
-          <t>BattlePower_Stat</t>
-        </is>
-      </c>
-      <c r="C1" s="9" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>!ID</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>SourceStat</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>Weight</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>!int</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>!Stat</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>!float</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="n"/>
-      <c r="B4" s="1" t="n">
+    <row r="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>Stat_Atk</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="n">
+      <c r="C1" s="9"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="4"/>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="4"/>
+      <c r="B3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="1" t="n">
+      <c r="D3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="7">
+        <v>6</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
         <v>2</v>
       </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>Stat_AtkSpeed</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5">
         <v>3300</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="1" t="n">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
         <v>3</v>
       </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>Stat_CritRate</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+      <c r="C6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6">
         <v>4600</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="1" t="n">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="1">
         <v>4</v>
       </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>Stat_CritDamage</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+      <c r="C7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7">
         <v>1400</v>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="1" t="n">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="1">
         <v>5</v>
       </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>Stat_DamageBonus</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="n">
+      <c r="C8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="7">
         <v>3750</v>
       </c>
-      <c r="E8" s="2" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="1" t="n">
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="1">
         <v>6</v>
       </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>Stat_MeleeDamageBonus</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="n">
+      <c r="C9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="7">
         <v>3750</v>
       </c>
-      <c r="E9" s="2" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="1" t="n">
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="1">
         <v>7</v>
       </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>Stat_RangeDamageBonus</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="n">
+      <c r="C10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="7">
         <v>3750</v>
       </c>
-      <c r="E10" s="2" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="1" t="n">
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="1">
         <v>8</v>
       </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>Stat_BossDamageBonus</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+      <c r="C11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11">
         <v>1100</v>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="1" t="n">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="1">
         <v>9</v>
       </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>Stat_FinalDamageAmp</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
+      <c r="C12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12">
         <v>5500</v>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="1" t="n">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="1">
         <v>10</v>
       </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>Stat_DefPen</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
+      <c r="C13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13">
         <v>2000</v>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="1" t="n">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="1">
         <v>11</v>
       </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>Stat_MaxHp</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
+      <c r="C14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14">
         <v>0.2</v>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="1" t="n">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="1">
         <v>12</v>
       </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>Stat_HpRegen</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
+      <c r="C15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15">
         <v>12</v>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="1" t="n">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="1">
         <v>13</v>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>Stat_Def</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
+      <c r="C16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16">
         <v>2.6</v>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="1" t="n">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="1">
         <v>14</v>
       </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>Stat_DamageReduction</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
+      <c r="C17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17">
         <v>5000</v>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="1" t="n">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" s="1">
         <v>15</v>
       </c>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>Stat_LifeOnHit</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
+      <c r="C18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18">
         <v>18</v>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="1" t="n">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="1">
         <v>16</v>
       </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>Stat_EvasionRate</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
+      <c r="C19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19">
         <v>4400</v>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="1" t="n">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="1">
         <v>17</v>
       </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>Stat_BlockRate</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
+      <c r="C20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20">
         <v>4400</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="1" t="n">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21" s="1">
         <v>18</v>
       </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>Stat_MoveSpeed</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
+      <c r="C21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21">
         <v>0</v>
       </c>
     </row>
-    <row r="26"/>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="11.625" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
-    <col width="19.25" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
-    <col width="23.75" customWidth="1" style="1" min="3" max="3"/>
-    <col width="16.25" customWidth="1" style="1" min="4" max="4"/>
-    <col width="16.5" customWidth="1" style="1" min="5" max="5"/>
-    <col width="13.75" customWidth="1" style="1" min="6" max="6"/>
-    <col width="13.625" customWidth="1" style="1" min="7" max="7"/>
-    <col width="18.5" customWidth="1" style="1" min="8" max="8"/>
-    <col width="9" customWidth="1" style="1" min="9" max="9"/>
-    <col width="9" customWidth="1" style="1" min="10" max="16384"/>
+    <col min="1" max="1" width="11.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5" style="1" customWidth="1"/>
+    <col min="9" max="10" width="9" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" s="3">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>!Table</t>
-        </is>
-      </c>
-      <c r="B1" s="9" t="inlineStr">
-        <is>
-          <t>BattlePower_Option</t>
-        </is>
-      </c>
-      <c r="C1" s="9" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>!ID</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>SourceOption</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>!int</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>!Option</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>!float</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="n"/>
-      <c r="B4" s="1" t="n">
+    <row r="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="9"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="4"/>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="4"/>
+      <c r="B3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="1">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>OPT_LEARN_DualBlades_Active_01</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="n">
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="7">
         <v>1500</v>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-    </row>
-    <row r="8">
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="2" t="n"/>
-    </row>
-    <row r="9">
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="2" t="n"/>
-    </row>
-    <row r="10">
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="2" t="n"/>
-    </row>
-    <row r="26"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D8" s="7"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D9" s="7"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D10" s="7"/>
+      <c r="E10" s="2"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/Shared/XLS/BattlePower.xlsx
+++ b/Shared/XLS/BattlePower.xlsx
@@ -107,7 +107,8 @@
     <t>!Option</t>
   </si>
   <si>
-    <t>OPT_LEARN_DualBlades_Active_01</t>
+    <t>OPT_LEARN_GreatSword_Active_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -539,7 +540,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
